--- a/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5CE93EF6-13E7-43E0-ABB5-3043AA10A0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE21F015-FEC4-4913-BB11-23B81CE7A56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="6120" windowWidth="23040" windowHeight="6120" xr2:uid="{5017E199-682B-44C1-BDFB-96C3EAAEAF45}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57F612BC-29D3-4C63-8F5B-823E75F4E7DC}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -27,17 +27,17 @@
     <sheet name="2.11 環境設定（テンプレート）" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（複数実行）'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'2.10 環境設定（グループ別）'!$A$1:$F$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'2.11 環境設定（テンプレート）'!$A$1:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（一括実行）'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（スペース作成）'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（スペースダウンロード）'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（設定ファイル作成）'!$A$1:$F$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 実行（スペース更新）'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 実行（スペース確認）'!$A$1:$F$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 ログ'!$A$1:$F$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（共通）'!$A$1:$F$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（複数実行）'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'2.10 環境設定（グループ別）'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'2.11 環境設定（テンプレート）'!$A$1:$G$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（一括実行）'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（スペース作成）'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（スペースダウンロード）'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（設定ファイル作成）'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 実行（スペース更新）'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 実行（スペース確認）'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 ログ'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（共通）'!$A$1:$G$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="162">
   <si>
     <t>通番</t>
   </si>
@@ -133,25 +133,32 @@
     <t>区分</t>
   </si>
   <si>
+    <t>入力値</t>
+  </si>
+  <si>
     <t>操作</t>
   </si>
   <si>
-    <t>期待結果</t>
+    <t>期待値</t>
   </si>
   <si>
     <t>参照</t>
   </si>
   <si>
-    <t>結果</t>
+    <t>実施結果</t>
   </si>
   <si>
     <t>正常系</t>
   </si>
   <si>
-    <t>有効な行がある実行一覧で、実行を押します。</t>
-  </si>
-  <si>
-    <t>行ごとに一括実行が行われ、実行ボタンの横に「終了（成功-N件、警告-N件、失敗/スキップ-N件）」と表示されます。</t>
+    <t>対象のグループ：ok
+実行一覧ファイル：run-list\ok.xlsx</t>
+  </si>
+  <si>
+    <t>実行を押します。</t>
+  </si>
+  <si>
+    <t>実行ボタンの横の状態：終了（成功-1件、警告-0件、失敗/スキップ-1件）</t>
   </si>
   <si>
     <t>画面設計 3.1、処理フロー 2.1</t>
@@ -163,88 +170,132 @@
     <t>実行が終わったあと、ログ欄を確認します。</t>
   </si>
   <si>
-    <t>実行結果のログが表示されます。ログの出力先に実行ログが保存されます。</t>
+    <t>ログ：実行結果が表示される
+ログの出力先：実行ログが保存される</t>
   </si>
   <si>
     <t>異常系</t>
   </si>
   <si>
-    <t>実行一覧ファイルを選ばずに、実行を押します。</t>
-  </si>
-  <si>
-    <t>メッセージが表示され、処理は実行されません。</t>
-  </si>
-  <si>
-    <t>スペース識別名が空の行がある実行一覧で、実行を押します。</t>
-  </si>
-  <si>
-    <t>その行はスキップされ、ほかの行だけが実行されます。</t>
-  </si>
-  <si>
-    <t>設定テンプレート（基本）とカスタムが両方空の行がある実行一覧で、実行を押します。</t>
-  </si>
-  <si>
-    <t>その行はスキップされます。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）の行がある実行一覧で、実行を押します。</t>
-  </si>
-  <si>
-    <t>行ごとに一括実行が行われ、ng の行は失敗と表示されます。</t>
+    <t>実行一覧ファイル：空</t>
+  </si>
+  <si>
+    <t>メッセージ：「実行一覧ファイルを選択してください」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+実行一覧ファイル：run-list\skip-identifier.xlsx</t>
+  </si>
+  <si>
+    <t>ログ：スペース識別名が空のためスキップします</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+実行一覧ファイル：run-list\skip-template.xlsx</t>
+  </si>
+  <si>
+    <t>ログ：いずれかが必要のためスキップ</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+実行一覧ファイル：run-list\ng.xlsx</t>
+  </si>
+  <si>
+    <t>ログ：終了（を含む）</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：batchok
+スペーステンプレートID：3</t>
+  </si>
+  <si>
+    <t>処理ごとの状態：成功</t>
+  </si>
+  <si>
+    <t>画面設計 3.2、処理フロー 2.2</t>
+  </si>
+  <si>
+    <t>表示／隠すを押します。</t>
+  </si>
+  <si>
+    <t>リンク：隠す、再度押すと表示</t>
+  </si>
+  <si>
+    <t>画面設計 3.2</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：skipok
+スペーステンプレートID：3
+スペースの作成：なし</t>
+  </si>
+  <si>
+    <t>スペースの作成の状態：スキップ
+ほかの処理の状態：成功または失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：logok
+スペーステンプレートID：3</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：空</t>
+  </si>
+  <si>
+    <t>メッセージ：「スペース識別名 を設定してください」
+処理：実行されない</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：TestId
+スペーステンプレートID：空</t>
+  </si>
+  <si>
+    <t>メッセージ：「スペーステンプレートID を設定してください」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：TestId
+スペーステンプレートID：TmplId
+設定テンプレート名（基本）：空
+設定テンプレート名（カスタム）：空</t>
+  </si>
+  <si>
+    <t>メッセージ：「設定テンプレート名（基本）または設定テンプレート名（カスタム）のどちらかを指定してください」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：failok
+スペーステンプレートID：99999</t>
+  </si>
+  <si>
+    <t>処理ごとの状態：失敗
+成功の表示：なし
+後続の処理：実行されない</t>
+  </si>
+  <si>
+    <t>画面設計 3.2、処理フロー 3</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+スペース識別名：ngtest
+スペーステンプレートID：3</t>
   </si>
   <si>
     <t>選んだ処理を実行します。</t>
   </si>
   <si>
-    <t>処理ごとに状態が表示され、状態に成功と表示されます。</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 2.2</t>
-  </si>
-  <si>
-    <t>表示／隠すを押します。</t>
-  </si>
-  <si>
-    <t>処理の選択欄が隠れ、もう一度押すと表示されます。</t>
-  </si>
-  <si>
-    <t>画面設計 3.2</t>
-  </si>
-  <si>
-    <t>スペースの作成のチェックを外し、ほかの処理にチェックを付けて、実行を押します。</t>
-  </si>
-  <si>
-    <t>スペースの作成はスキップと表示され、チェックの付いた処理だけが実行されます。</t>
-  </si>
-  <si>
-    <t>スペース識別名を空にして、実行を押します。</t>
-  </si>
-  <si>
-    <t>スペーステンプレートIDを空にして、実行を押します。</t>
-  </si>
-  <si>
-    <t>設定テンプレート（基本）とカスタムを両方とも選ばずに、実行を押します。</t>
-  </si>
-  <si>
-    <t>途中の処理が失敗するように準備して、実行を押します。</t>
-  </si>
-  <si>
-    <t>失敗した処理の後続の処理は実行されません。</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 3</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、選んだ処理を実行します。</t>
-  </si>
-  <si>
-    <t>状態に失敗と表示されます。</t>
-  </si>
-  <si>
-    <t>スペース識別名とスペーステンプレートIDを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>スペースが作成され、状態に成功と表示されます。作成したスペースのIDが、スペースダウンロードの「スペースID」に入ります。</t>
+    <t>状態：失敗</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：createok
+スペーステンプレートID：3</t>
+  </si>
+  <si>
+    <t>状態：成功
+スペースID：数字（作成されたID）</t>
   </si>
   <si>
     <t>画面設計 3.3、処理フロー 2.3</t>
@@ -253,22 +304,29 @@
     <t>開くを押します。</t>
   </si>
   <si>
-    <t>kintone の画面が、ブラウザで開きます。</t>
+    <t>開いた画面：createok（ブラウザ）</t>
   </si>
   <si>
     <t>画面設計 3.3</t>
   </si>
   <si>
-    <t>スペース識別名またはスペーステンプレートIDを空にして、実行を押します。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）で、スペースの作成を実行します。</t>
-  </si>
-  <si>
-    <t>スペース識別名とスペースIDを入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に成功と表示され、ダウンロード結果の Excel が作られます。</t>
+    <t>対象のグループ：ok
+スペース識別名：空
+スペーステンプレートID：空</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+スペース識別名：createng
+スペーステンプレートID：2</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：dlok
+スペースID：3</t>
+  </si>
+  <si>
+    <t>状態：成功
+ファイル：download\dlok_download.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計 3.4、処理フロー 2.4</t>
@@ -277,217 +335,278 @@
     <t>実行が完了したあと、開くを押します。</t>
   </si>
   <si>
-    <t>ダウンロード結果の Excel が開きます。</t>
+    <t>開いた画面：dlok_download（Excel）</t>
   </si>
   <si>
     <t>画面設計 3.4</t>
   </si>
   <si>
-    <t>異常のクライアント（ng）で、スペースダウンロードを実行します。</t>
-  </si>
-  <si>
-    <t>設定テンプレートを選び、スペース識別名を入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に成功または警告と表示され、設定ファイルが作られます。</t>
+    <t>対象のグループ：ng
+スペース識別名：dlng
+スペースID：3</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：dlok
+設定テンプレート名（基本）：3</t>
+  </si>
+  <si>
+    <t>状態：成功
+ファイル：config\dlok_config.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計 3.5、処理フロー 2.5</t>
   </si>
   <si>
-    <t>設定ファイルが開きます。</t>
+    <t>開いた画面：dlok_config（Excel）</t>
   </si>
   <si>
     <t>画面設計 3.5</t>
   </si>
   <si>
-    <t>異常のクライアント（ng）で、設定ファイルの作成を実行します。</t>
-  </si>
-  <si>
-    <t>設定ファイルがある状態で、実行を押します。</t>
-  </si>
-  <si>
-    <t>設定ファイルの内容が kintone のスペースに反映され、状態に成功と表示されます。</t>
+    <t>対象のグループ：ok
+スペース識別名：TestId
+設定テンプレート名（基本）：空
+設定テンプレート名（カスタム）：空</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+スペース識別名：cfgng</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：dlok</t>
+  </si>
+  <si>
+    <t>状態：成功</t>
   </si>
   <si>
     <t>画面設計 3.6、処理フロー 2.6</t>
   </si>
   <si>
+    <t>開いた画面：dlok（ブラウザ）</t>
+  </si>
+  <si>
     <t>画面設計 3.6</t>
   </si>
   <si>
-    <t>異常のクライアント（ng）で、スペース更新を実行します。</t>
-  </si>
-  <si>
-    <t>状態に成功と表示され、チェック結果の Excel が作られます。</t>
+    <t>対象のグループ：ng
+スペース識別名：updng</t>
+  </si>
+  <si>
+    <t>状態：成功
+ファイル：checked\dlok_check.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計 3.7、処理フロー 2.7</t>
   </si>
   <si>
-    <t>チェック結果の Excel が開きます。</t>
+    <t>開いた画面：dlok_check（Excel）</t>
   </si>
   <si>
     <t>画面設計 3.7</t>
   </si>
   <si>
-    <t>異常のクライアント（ng）で、スペース確認を実行します。</t>
-  </si>
-  <si>
-    <t>ログのファイルがない状態で、すべて削除を押します。</t>
-  </si>
-  <si>
-    <t>「削除対象のログファイルがありません」と表示されます（文言は（未確認））。</t>
+    <t>対象のグループ：ng
+スペース識別名：chkng</t>
+  </si>
+  <si>
+    <t>すべて削除を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「削除対象のログファイルがありません」</t>
   </si>
   <si>
     <t>画面設計 3.8、処理フロー 2.8</t>
   </si>
   <si>
-    <t>ログのファイルがある状態で、すべて削除を押し、確認で「いいえ」を選びます。</t>
-  </si>
-  <si>
-    <t>何も削除されず、ログのファイルは残ります。</t>
-  </si>
-  <si>
-    <t>ログのファイルがある状態で、すべて削除を押し、確認で「はい」を選びます。</t>
-  </si>
-  <si>
-    <t>ログのファイルがすべて削除されます。</t>
-  </si>
-  <si>
-    <t>対象のグループで「すべて」を選ぶと両方のログが表示され、「ok」を選ぶと ok のログだけが表示されます。</t>
-  </si>
-  <si>
-    <t>そのグループの実行ログだけが表示されます。</t>
+    <t>確認：いいえ</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログのファイル：残る</t>
+  </si>
+  <si>
+    <t>確認：はい</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログのファイル：すべて削除される</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて、ok、ng</t>
+  </si>
+  <si>
+    <t>対象のグループを選びます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ、「ng」を選ぶと ng のログだけ</t>
   </si>
   <si>
     <t>画面設計 3.8</t>
   </si>
   <si>
-    <t>スペース識別名（ログの絞り込み）で、すべてを選ぶと両方のログが表示され、okを選ぶとokのログだけが表示されます。</t>
-  </si>
-  <si>
-    <t>上記のとおりに表示されます。</t>
+    <t>スペース識別名（ログの絞り込み）：すべて、config1、config2</t>
+  </si>
+  <si>
+    <t>スペース識別名（ログの絞り込み）を選びます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」を選ぶと両方、「config1」を選ぶと config1 のログだけ、「config2」を選ぶと config2 のログだけ</t>
   </si>
   <si>
     <t>処理のラジオボタンを切り替えます。</t>
   </si>
   <si>
-    <t>選んだ処理のログだけが表示されます。</t>
-  </si>
-  <si>
-    <t>フォルダの場所を変えて、保存を押します。</t>
-  </si>
-  <si>
-    <t>変えた値が保存され、画面の表示が保存後の内容に更新されます。</t>
+    <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
+  </si>
+  <si>
+    <t>ダウンロード先のフォルダ：%BASE_PATH%download2</t>
+  </si>
+  <si>
+    <t>保存を押します。</t>
+  </si>
+  <si>
+    <t>状態：完了
+保存先：bats\common.bat に download2 が保存される</t>
   </si>
   <si>
     <t>画面設計 3.9、処理フロー 2.9</t>
   </si>
   <si>
-    <t>フォルダの場所を変えたあと、再読込を押します。</t>
-  </si>
-  <si>
-    <t>保存されている値で入力欄が表示し直され、変えた内容は消えます。</t>
+    <t>ダウンロード先のフォルダ：tmp</t>
+  </si>
+  <si>
+    <t>再読込を押します。</t>
+  </si>
+  <si>
+    <t>入力欄：%BASE_PATH%download（保存されている値）
+変えた内容：消える</t>
   </si>
   <si>
     <t>画面設計 3.9、処理フロー 2.10</t>
   </si>
   <si>
-    <t>新規作成を押し、既存のグループと同じ名前を入力します。</t>
-  </si>
-  <si>
-    <t>「「（入力した名前）」は既に存在します。」と表示され、グループは追加されません。</t>
+    <t>新しい名前：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>新規作成を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」
+一覧：追加されない</t>
   </si>
   <si>
     <t>画面設計 3.10、処理フロー 2.11</t>
   </si>
   <si>
-    <t>新規作成を押し、新しい名前を入力します。</t>
-  </si>
-  <si>
-    <t>名前が対象のグループの一覧に追加され、選ばれます。</t>
+    <t>新しい名前：KrgNew</t>
+  </si>
+  <si>
+    <t>一覧：KrgNew が追加され、選ばれる</t>
   </si>
   <si>
     <t>新規作成を押したあと、キャンセルを押します。</t>
   </si>
   <si>
-    <t>一覧は変わりません。</t>
-  </si>
-  <si>
-    <t>新規作成直後の、まだ保存していないグループを選び、コピーを押します。</t>
-  </si>
-  <si>
-    <t>「コピー元のグループが存在しません」と表示され、コピーは行われません。</t>
+    <t>ファイル：clients\KrgCancel.bat が作られない
+一覧：変わらない</t>
+  </si>
+  <si>
+    <t>新しい名前：KrgUnsaved</t>
+  </si>
+  <si>
+    <t>コピーを押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません」
+ファイル：clients\KrgUnsaved.bat が作られる</t>
   </si>
   <si>
     <t>画面設計 3.10、処理フロー 2.12</t>
   </si>
   <si>
-    <t>保存済みのグループを選び、コピーを押して、新しい名前を入力します。</t>
-  </si>
-  <si>
-    <t>新しいグループが一覧に 1 つだけ追加され、選ばれます。設定ファイルがコピーされます。</t>
-  </si>
-  <si>
-    <t>入力欄の値を変えて、保存を押します。</t>
-  </si>
-  <si>
-    <t>値が設定ファイルに保存され、画面の表示が保存後の内容に更新されます。</t>
+    <t>対象のグループ：ok
+新しい名前：KrgCopy</t>
+  </si>
+  <si>
+    <t>一覧：KrgCopy が追加され、選ばれる
+ファイル：clients\KrgCopy.bat が作られる</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：saved</t>
+  </si>
+  <si>
+    <t>状態：完了
+ファイル：clients\ok.bat に saved が保存される</t>
   </si>
   <si>
     <t>画面設計 3.10、処理フロー 2.13</t>
   </si>
   <si>
-    <t>入力欄の値を変えたあと、再読込を押します。</t>
+    <t>対象のグループ：ok
+サブドメイン：tmp</t>
+  </si>
+  <si>
+    <t>入力欄：iiglepv0966f（保存されている値）
+変えた内容：消える</t>
   </si>
   <si>
     <t>画面設計 3.10、処理フロー 2.14</t>
   </si>
   <si>
-    <t>正しい接続情報で、テスト接続を押します。</t>
-  </si>
-  <si>
-    <t>状態に成功と表示されます。</t>
+    <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
+  </si>
+  <si>
+    <t>テスト接続を押します。</t>
   </si>
   <si>
     <t>画面設計 3.10、処理フロー 2.15</t>
   </si>
   <si>
-    <t>コピーを押し、既存のグループと同じ名前を入力します。</t>
-  </si>
-  <si>
-    <t>「「（入力した名前）」は既に存在します。」と表示され、コピーは行われません。</t>
-  </si>
-  <si>
-    <t>kintone接続のサブドメインを空にして、テスト接続を押します。</t>
-  </si>
-  <si>
-    <t>状態に失敗と表示され、接続は行われません。</t>
-  </si>
-  <si>
-    <t>誤ったパスワードで、テスト接続を押します。</t>
-  </si>
-  <si>
-    <t>異常のクライアント（ng）を選び、誤ったパスワードを入力して、テスト接続を押します。</t>
-  </si>
-  <si>
-    <t>対象のグループ、スペースID、テンプレート名を入力して、実行を押します。</t>
-  </si>
-  <si>
-    <t>状態に成功と表示され、テンプレートのファイルが作られます。</t>
+    <t>対象のグループ：ok
+新しい名前：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：空</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パスワード：wrong-password</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+パスワード：wrong-password</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペースID：3
+テンプレート名：ok</t>
+  </si>
+  <si>
+    <t>状態：成功
+ファイル：template\custom\ok_ok.xlsx が作られる</t>
   </si>
   <si>
     <t>画面設計 3.11、処理フロー 2.16</t>
   </si>
   <si>
-    <t>テンプレートのファイルが開きます。</t>
+    <t>開いた画面：ok_ok（Excel）</t>
   </si>
   <si>
     <t>画面設計 3.11</t>
   </si>
   <si>
-    <t>対象のグループ、スペースID、テンプレート名をすべて空にして、実行を押します。</t>
+    <t>対象のグループ、スペースID
+テンプレート名：すべて空</t>
+  </si>
+  <si>
+    <t>メッセージ：「対象のグループ、スペースID、テンプレート名を入力してください」</t>
   </si>
 </sst>
 </file>
@@ -886,7 +1005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9982F465-A9C3-4F9B-A87B-28E560049121}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F50C9B-8B0D-4089-9E99-8B124057C5E4}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1028,26 +1147,27 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12" xr:uid="{9982F465-A9C3-4F9B-A87B-28E560049121}"/>
+  <autoFilter ref="A1:C12" xr:uid="{D8F50C9B-8B0D-4089-9E99-8B124057C5E4}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAB544D-5A74-4BF2-A677-B7C73AA0104A}">
-  <dimension ref="A1:F3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A63DA1-8A5E-4530-887D-ED80C884B652}">
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1066,68 +1186,78 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
+        <v>126</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F3" xr:uid="{FAAB544D-5A74-4BF2-A677-B7C73AA0104A}"/>
+  <autoFilter ref="A1:G3" xr:uid="{B8A63DA1-8A5E-4530-887D-ED80C884B652}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93E6B676-E426-431D-9EE6-E93A89A30D0D}">
-  <dimension ref="A1:F13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CA04723-DA52-4D5D-B06B-713DFB053CF9}">
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1146,268 +1276,308 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>37</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>143</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>146</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>138</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>62</v>
+        <v>148</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>149</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F13" xr:uid="{93E6B676-E426-431D-9EE6-E93A89A30D0D}"/>
+  <autoFilter ref="A1:G13" xr:uid="{6CA04723-DA52-4D5D-B06B-713DFB053CF9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF550118-278C-4D51-8BC6-A5F5C565AB85}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07F9D6E-DC64-4B36-B1F8-3632DDE7D1D9}">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1426,88 +1596,101 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>157</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>159</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>157</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4" xr:uid="{BF550118-278C-4D51-8BC6-A5F5C565AB85}"/>
+  <autoFilter ref="A1:G4" xr:uid="{F07F9D6E-DC64-4B36-B1F8-3632DDE7D1D9}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE7497B-D69A-4F22-A4A4-60BC5C648448}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2EB034-3901-4859-8B5D-8AC8473A78E0}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1526,148 +1709,170 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="252" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7" xr:uid="{6FE7497B-D69A-4F22-A4A4-60BC5C648448}"/>
+  <autoFilter ref="A1:G7" xr:uid="{EF2EB034-3901-4859-8B5D-8AC8473A78E0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CC9C08B-0FE3-41FF-8392-B170C4D344B2}">
-  <dimension ref="A1:F10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4371BDB-1634-48AC-AFC4-53E0821441DF}">
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1686,208 +1891,239 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="198" x14ac:dyDescent="0.45">
+        <v>54</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="360" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>51</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>66</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
+        <v>51</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F10" xr:uid="{7CC9C08B-0FE3-41FF-8392-B170C4D344B2}"/>
+  <autoFilter ref="A1:G10" xr:uid="{B4371BDB-1634-48AC-AFC4-53E0821441DF}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7630FAC0-A2A9-4886-ABE5-0491D1DAAC48}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47E84BA-7759-477A-B660-7A2B35411083}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1906,108 +2142,124 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="270" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>75</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>72</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>72</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5" xr:uid="{7630FAC0-A2A9-4886-ABE5-0491D1DAAC48}"/>
+  <autoFilter ref="A1:G5" xr:uid="{B47E84BA-7759-477A-B660-7A2B35411083}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7034C734-5567-471C-B03C-6DB33C373C86}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A730DC49-937B-49FB-AC66-4BE4ED439C97}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2026,108 +2278,124 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>83</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>80</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5" xr:uid="{7034C734-5567-471C-B03C-6DB33C373C86}"/>
+  <autoFilter ref="A1:G5" xr:uid="{A730DC49-937B-49FB-AC66-4BE4ED439C97}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8207021A-77FC-4E62-BC31-B6B0556CF6FA}">
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF84B593-1D90-44E3-8E03-C548867561BA}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2146,128 +2414,147 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>81</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>89</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="162" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+        <v>87</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F6" xr:uid="{8207021A-77FC-4E62-BC31-B6B0556CF6FA}"/>
+  <autoFilter ref="A1:G6" xr:uid="{AF84B593-1D90-44E3-8E03-C548867561BA}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6858384-48D0-40F2-BEA7-844BC3F602C1}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C049101B-C07A-47BD-AE85-FEECA21EE90E}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2286,108 +2573,124 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>96</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>94</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>94</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5" xr:uid="{D6858384-48D0-40F2-BEA7-844BC3F602C1}"/>
+  <autoFilter ref="A1:G5" xr:uid="{C049101B-C07A-47BD-AE85-FEECA21EE90E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7051887D-B50B-4832-BBB0-C757B1D3F421}">
-  <dimension ref="A1:F5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFEC446-5B8B-4116-B077-4F7AD7289CC0}">
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2406,108 +2709,124 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="108" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="126" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
+        <v>99</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5" xr:uid="{7051887D-B50B-4832-BBB0-C757B1D3F421}"/>
+  <autoFilter ref="A1:G5" xr:uid="{2CFEC446-5B8B-4116-B077-4F7AD7289CC0}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BB5979C-1EBA-4216-B95D-E30FCFC8200E}">
-  <dimension ref="A1:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495A2F42-D793-46FE-8656-BF6F6AB47715}">
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="45.69921875" customWidth="1"/>
-    <col min="4" max="4" width="60.69921875" customWidth="1"/>
-    <col min="5" max="5" width="28.69921875" customWidth="1"/>
-    <col min="6" max="6" width="10.69921875" customWidth="1"/>
+    <col min="3" max="3" width="50.69921875" customWidth="1"/>
+    <col min="4" max="4" width="45.69921875" customWidth="1"/>
+    <col min="5" max="5" width="75.69921875" customWidth="1"/>
+    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2526,129 +2845,150 @@
       <c r="F1" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+      <c r="G1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>105</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="180" x14ac:dyDescent="0.45">
+        <v>105</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="252" x14ac:dyDescent="0.45">
+        <v>105</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="270" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>113</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7" xr:uid="{8BB5979C-1EBA-4216-B95D-E30FCFC8200E}"/>
+  <autoFilter ref="A1:G7" xr:uid="{495A2F42-D793-46FE-8656-BF6F6AB47715}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE21F015-FEC4-4913-BB11-23B81CE7A56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F14DB658-970B-4161-B8F8-15012C21880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57F612BC-29D3-4C63-8F5B-823E75F4E7DC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{255AE821-CC83-4DEC-8291-52AC6F6926E6}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -28,16 +28,16 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（複数実行）'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'2.10 環境設定（グループ別）'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'2.10 環境設定（グループ別）'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'2.11 環境設定（テンプレート）'!$A$1:$G$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（一括実行）'!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（一括実行）'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'2.3 実行（スペース作成）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'2.4 実行（スペースダウンロード）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'2.5 実行（設定ファイル作成）'!$A$1:$G$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 実行（スペース更新）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 実行（スペース確認）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 ログ'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（共通）'!$A$1:$G$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（共通）'!$A$1:$G$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="230">
   <si>
     <t>通番</t>
   </si>
@@ -115,13 +115,16 @@
     <t>環境設定（共通）</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
     <t>環境設定（グループ別）</t>
   </si>
   <si>
-    <t>12</t>
+    <t>16</t>
   </si>
   <si>
     <t>11</t>
@@ -152,461 +155,833 @@
   </si>
   <si>
     <t>対象のグループ：ok
-実行一覧ファイル：run-list\ok.xlsx</t>
-  </si>
-  <si>
-    <t>実行を押します。</t>
-  </si>
-  <si>
-    <t>実行ボタンの横の状態：終了（成功-1件、警告-0件、失敗/スキップ-1件）</t>
-  </si>
-  <si>
-    <t>画面設計 3.1、処理フロー 2.1</t>
+実行一覧ファイル：ok.xlsx
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「実行一覧ファイル」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態：終了（成功-1件、警告-0件、失敗/スキップ-1件）</t>
+  </si>
+  <si>
+    <t>画面設計：3.1
+処理フロー：2.1</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>実行が終わったあと、ログ欄を確認します。</t>
-  </si>
-  <si>
-    <t>ログ：実行結果が表示される
-ログの出力先：実行ログが保存される</t>
+    <t>状態：終了（件数）が表示される</t>
   </si>
   <si>
     <t>異常系</t>
   </si>
   <si>
-    <t>実行一覧ファイル：空</t>
-  </si>
-  <si>
-    <t>メッセージ：「実行一覧ファイルを選択してください」</t>
+    <t>対象のグループ：ng
+実行一覧ファイル：空
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「実行一覧ファイルを選択してください。」</t>
   </si>
   <si>
     <t>対象のグループ：ok
-実行一覧ファイル：run-list\skip-identifier.xlsx</t>
-  </si>
-  <si>
-    <t>ログ：スペース識別名が空のためスキップします</t>
+実行一覧ファイル：skip-identifier.xlsx
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態：終了（成功-0件、警告-0件、失敗/スキップ-1件）</t>
   </si>
   <si>
     <t>対象のグループ：ok
-実行一覧ファイル：run-list\skip-template.xlsx</t>
-  </si>
-  <si>
-    <t>ログ：いずれかが必要のためスキップ</t>
+実行一覧ファイル：skip-template.xlsx
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>対象のグループ：ng
-実行一覧ファイル：run-list\ng.xlsx</t>
-  </si>
-  <si>
-    <t>ログ：終了（を含む）</t>
+実行一覧ファイル：ng.xlsx
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>状態：終了（成功-0件、警告-0件、失敗/スキップ-1件以上）</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：batchok
-スペーステンプレートID：3</t>
-  </si>
-  <si>
-    <t>処理ごとの状態：成功</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 2.2</t>
-  </si>
-  <si>
-    <t>表示／隠すを押します。</t>
+スペース識別名：TestSpace
+スペーステンプレートID：3
+設定テンプレート名（基本）：クラススペース
+設定テンプレート名（カスタム）：空
+スペースの作成：あり
+スペースのダウンロード：あり
+設定ファイルの作成：あり
+スペースの更新：あり
+スペースの確認：あり
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」と「スペーステンプレートID」と「設定テンプレート名（基本）」を設定した後で、「表示／隠す」を押した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功
+状態（スペースの作成）：成功
+状態（スペースのダウンロード）：成功
+状態（設定ファイルの作成）：成功
+状態（スペースの更新）：成功
+状態（スペースの確認）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.2
+処理フロー：2.2</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：空
+スペーステンプレートID：空
+設定テンプレート名（基本）：空
+設定テンプレート名（カスタム）：空
+スペースの作成：あり
+スペースのダウンロード：あり
+設定ファイルの作成：あり
+スペースの更新：あり
+スペースの確認：あり
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「表示／隠す」を押した後で、「表示／隠す」を押します。</t>
   </si>
   <si>
     <t>リンク：隠す、再度押すと表示</t>
   </si>
   <si>
-    <t>画面設計 3.2</t>
+    <t>画面設計：3.2</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：skipok
+スペース識別名：TestSpace
 スペーステンプレートID：3
-スペースの作成：なし</t>
-  </si>
-  <si>
-    <t>スペースの作成の状態：スキップ
-ほかの処理の状態：成功または失敗</t>
+設定テンプレート名（基本）：クラススペース
+設定テンプレート名（カスタム）：空
+スペースの作成：あり
+スペースのダウンロード：あり
+設定ファイルの作成：あり
+スペースの更新：あり
+スペースの確認：なし
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」と「スペーステンプレートID」と「設定テンプレート名（基本）」を設定した後で、「表示／隠す」を押した後で、「スペースの確認」のチェックを外して、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功
+状態（スペースの確認）：スキップ
+状態（スペースのダウンロード）：成功または失敗</t>
+  </si>
+  <si>
+    <t>メッセージ：「スペース識別名 を設定してください。」</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：logok
-スペーステンプレートID：3</t>
+スペース識別名：TestSpace
+スペーステンプレートID：空
+設定テンプレート名（基本）：空
+設定テンプレート名（カスタム）：空
+スペースの作成：あり
+スペースのダウンロード：あり
+設定ファイルの作成：あり
+スペースの更新：あり
+スペースの確認：あり
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「スペーステンプレートID を設定してください。」</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：空</t>
-  </si>
-  <si>
-    <t>メッセージ：「スペース識別名 を設定してください」
-処理：実行されない</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-スペース識別名：TestId
-スペーステンプレートID：空</t>
-  </si>
-  <si>
-    <t>メッセージ：「スペーステンプレートID を設定してください」</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-スペース識別名：TestId
+スペース識別名：TestSpace
 スペーステンプレートID：TmplId
 設定テンプレート名（基本）：空
-設定テンプレート名（カスタム）：空</t>
-  </si>
-  <si>
-    <t>メッセージ：「設定テンプレート名（基本）または設定テンプレート名（カスタム）のどちらかを指定してください」</t>
+設定テンプレート名（カスタム）：空
+スペースの作成：あり
+スペースのダウンロード：あり
+設定ファイルの作成：あり
+スペースの更新：あり
+スペースの確認：あり
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」と「スペーステンプレートID」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「設定テンプレート名（基本）または設定テンプレート名（カスタム）のどちらかを指定してください。」</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：failok
-スペーステンプレートID：99999</t>
-  </si>
-  <si>
-    <t>処理ごとの状態：失敗
-成功の表示：なし
-後続の処理：実行されない</t>
-  </si>
-  <si>
-    <t>画面設計 3.2、処理フロー 3</t>
+スペース識別名：TestSpace
+スペーステンプレートID：99999
+設定テンプレート名（基本）：クラススペース
+設定テンプレート名（カスタム）：空
+スペースの作成：あり
+スペースのダウンロード：あり
+設定ファイルの作成：あり
+スペースの更新：あり
+スペースの確認：あり
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態：失敗
+状態（スペースの作成）：失敗
+状態（設定ファイルの作成）：表示されない</t>
   </si>
   <si>
     <t>対象のグループ：ng
-スペース識別名：ngtest
-スペーステンプレートID：3</t>
-  </si>
-  <si>
-    <t>選んだ処理を実行します。</t>
+スペース識別名：TestSpace
+スペーステンプレートID：3
+設定テンプレート名（基本）：クラススペース
+設定テンプレート名（カスタム）：空
+スペースの作成：あり
+スペースのダウンロード：あり
+設定ファイルの作成：あり
+スペースの更新：あり
+スペースの確認：あり
+設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>状態：失敗</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：createok
-スペーステンプレートID：3</t>
+スペース識別名：TestSpace
+スペーステンプレートID：3
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行」を実行し、「スペースダウンロード」タブを選びます。</t>
   </si>
   <si>
     <t>状態：成功
-スペースID：数字（作成されたID）</t>
-  </si>
-  <si>
-    <t>画面設計 3.3、処理フロー 2.3</t>
-  </si>
-  <si>
-    <t>開くを押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：createok（ブラウザ）</t>
-  </si>
-  <si>
-    <t>画面設計 3.3</t>
+スペースID（スペースダウンロード）：数字（作成されたID）</t>
+  </si>
+  <si>
+    <t>画面設計：3.3
+処理フロー：2.3</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」と「スペーステンプレートID」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：TestSpace（ブラウザ）</t>
+  </si>
+  <si>
+    <t>画面設計：3.3</t>
   </si>
   <si>
     <t>対象のグループ：ok
 スペース識別名：空
-スペーステンプレートID：空</t>
+スペーステンプレートID：空
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>対象のグループ：ng
-スペース識別名：createng
-スペーステンプレートID：2</t>
+スペース識別名：TestSpace
+スペーステンプレートID：2
+設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：dlok
-スペースID：3</t>
+スペース識別名：TestSpace
+スペースID：3
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」と「スペースID」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
-ファイル：download\dlok_download.xlsx が作られる</t>
-  </si>
-  <si>
-    <t>画面設計 3.4、処理フロー 2.4</t>
-  </si>
-  <si>
-    <t>実行が完了したあと、開くを押します。</t>
-  </si>
-  <si>
-    <t>開いた画面：dlok_download（Excel）</t>
-  </si>
-  <si>
-    <t>画面設計 3.4</t>
+ファイル：TestSpace_download.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.4
+処理フロー：2.4</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」と「スペースID」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
+  </si>
+  <si>
+    <t>開いた画面：TestSpace_download（Excel）</t>
+  </si>
+  <si>
+    <t>画面設計：3.4</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：空
+スペースID：空
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>対象のグループ：ng
-スペース識別名：dlng
-スペースID：3</t>
+スペース識別名：TestSpace
+スペースID：3
+設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：dlok
-設定テンプレート名（基本）：3</t>
+スペース識別名：TestSpace
+スペースID：3
+設定テンプレート名（基本）：クラススペース
+設定テンプレート名（カスタム）：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（スペースダウンロード）」を実行し、「対象のグループ」と「スペース識別名」と「設定テンプレート名（基本）」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+ファイル：TestSpace_config.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.5
+処理フロー：2.5</t>
+  </si>
+  <si>
+    <t>「実行（スペースダウンロード）」を実行し、「対象のグループ」と「スペース識別名」と「設定テンプレート名（基本）」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功または警告
+開いた画面：TestSpace_config（Excel）</t>
+  </si>
+  <si>
+    <t>画面設計：3.5</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：空
+設定テンプレート名（基本）：空
+設定テンプレート名（カスタム）：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：TestSpace
+設定テンプレート名（基本）：空
+設定テンプレート名（カスタム）：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+スペース識別名：TestSpace
+設定テンプレート名（基本）：クラススペース
+設定テンプレート名（カスタム）：空
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」と「設定テンプレート名（基本）」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+スペース識別名：TestSpace
+スペースID：3
+設定テンプレート名（基本）：クラススペース
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「実行（スペースダウンロード）」を実行し、「対象のグループ」と「スペース識別名」と「設定テンプレート名（基本）」を設定した後で、「実行（設定ファイル作成）」を押した後で、「対象のグループ」と「スペース識別名」を設定した後で、「実行」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.6
+処理フロー：2.6</t>
+  </si>
+  <si>
+    <t>「実行（スペースダウンロード）」を実行し、「対象のグループ」と「スペース識別名」と「設定テンプレート名（基本）」を設定した後で、「実行（設定ファイル作成）」を押した後で、「対象のグループ」と「スペース識別名」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
   </si>
   <si>
     <t>状態：成功
-ファイル：config\dlok_config.xlsx が作られる</t>
-  </si>
-  <si>
-    <t>画面設計 3.5、処理フロー 2.5</t>
-  </si>
-  <si>
-    <t>開いた画面：dlok_config（Excel）</t>
-  </si>
-  <si>
-    <t>画面設計 3.5</t>
+開いた画面：TestSpace（ブラウザ）</t>
+  </si>
+  <si>
+    <t>画面設計：3.6</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：TestId
-設定テンプレート名（基本）：空
-設定テンプレート名（カスタム）：空</t>
+スペース識別名：空
+設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>対象のグループ：ng
-スペース識別名：cfgng</t>
+スペース識別名：TestSpace
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>状態：成功
+ファイル：TestSpace_check.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.7
+処理フロー：2.7</t>
+  </si>
+  <si>
+    <t>状態：成功
+開いた画面：TestSpace_check（Excel）</t>
+  </si>
+  <si>
+    <t>画面設計：3.7</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+確認：いいえ
+スペース識別名：すべて
+処理：スペースの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」を設定した後で、ログのファイルがある状態で、「すべて削除」を押し、確認で「いいえ」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：残る</t>
+  </si>
+  <si>
+    <t>画面設計：3.8
+処理フロー：2.8</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+確認：はい
+スペース識別名：すべて
+処理：スペースの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」を設定した後で、ログのファイルがある状態で、「すべて削除」を押し、確認で「はい」を押します。</t>
+  </si>
+  <si>
+    <t>確認ダイアログ：ログファイルを削除します
+ログ：すべて削除される</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて、ok、ng
+スペース識別名：すべて
+処理：スペースの作成</t>
+  </si>
+  <si>
+    <t>「スペース識別名」を設定した後で、「対象のグループ」を切り替えます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ、「ng」を選ぶと ng のログだけ</t>
+  </si>
+  <si>
+    <t>画面設計：3.8</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+スペース識別名：すべて、config1、config2
+処理：スペースの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「スペース識別名」を切り替えます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：「すべて」を選ぶと両方、「config1」を選ぶと config1 のログだけ、「config2」を選ぶと config2 のログだけ</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+スペース識別名：すべて
+処理：スペースの作成、スペースのダウンロード、設定ファイルの作成、スペースの更新、スペースの確認</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」を設定した後で、「処理」のラジオボタンを「スペースの作成」、「スペースのダウンロード」、「設定ファイルの作成」、「スペースの更新」、「スペースの確認」、「スペースの作成」の順に切り替えます。</t>
+  </si>
+  <si>
+    <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
+  </si>
+  <si>
+    <t>対象のグループ：すべて
+スペース識別名：すべて
+処理：スペースの作成</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペース識別名」を設定した後で、ログのファイルがない状態で、「すべて削除」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「削除対象のログファイルがありません。」</t>
+  </si>
+  <si>
+    <t>ダウンロード先のフォルダ：saved-download-path</t>
+  </si>
+  <si>
+    <t>「ダウンロード先のフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>状態（保存）：完了
+保存先：common.bat に saved-download-path が保存される</t>
+  </si>
+  <si>
+    <t>画面設計：3.9
+処理フロー：2.9</t>
+  </si>
+  <si>
+    <t>ダウンロード先のフォルダ：tmp-reload</t>
+  </si>
+  <si>
+    <t>「ダウンロード先のフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>入力欄：（保存されている値）
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>画面設計：3.9
+処理フロー：2.10</t>
+  </si>
+  <si>
+    <t>設定テンプレート（基本）ファイルのフォルダ：saved-base-template
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「設定テンプレート（基本）ファイルのフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-base-template が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>設定テンプレート（基本）ファイルのフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「設定テンプレート（基本）ファイルのフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>設定テンプレート（基本）ファイルのフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>設定テンプレート（カスタム）ファイルのフォルダ：saved-custom-template
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「設定テンプレート（カスタム）ファイルのフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-custom-template が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>設定テンプレート（カスタム）ファイルのフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「設定テンプレート（カスタム）ファイルのフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>設定テンプレート（カスタム）ファイルのフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>設定ファイルのフォルダ：saved-config-folder
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「設定ファイルのフォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-config-folder が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>設定ファイルのフォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「設定ファイルのフォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイルのフォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>チェック結果の出力先フォルダ：saved-check-output
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「チェック結果の出力先フォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-check-output が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>チェック結果の出力先フォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「チェック結果の出力先フォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>チェック結果の出力先フォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>ログの出力先フォルダ：saved-log-folder
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「ログの出力先フォルダ」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：common.bat に saved-log-folder が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>ログの出力先フォルダ：tmp-reload
+設定ファイル：common.bat</t>
+  </si>
+  <si>
+    <t>「ログの出力先フォルダ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログの出力先フォルダ：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>状態（再読込）：完了</t>
   </si>
   <si>
     <t>対象のグループ：ok
-スペース識別名：dlok</t>
-  </si>
-  <si>
-    <t>状態：成功</t>
-  </si>
-  <si>
-    <t>画面設計 3.6、処理フロー 2.6</t>
-  </si>
-  <si>
-    <t>開いた画面：dlok（ブラウザ）</t>
-  </si>
-  <si>
-    <t>画面設計 3.6</t>
+設定ファイル：ok.bat
+グループ名：TestNew</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>一覧：TestNew が追加され、選ばれる</t>
+  </si>
+  <si>
+    <t>画面設計：3.10
+処理フロー：2.11</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押した後で、「キャンセル」を押します。</t>
+  </si>
+  <si>
+    <t>ファイル：TestCancel.bat が作られない</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：TestCopy</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「コピー」を押し、「グループ名」を入力して「OK」を押します。</t>
+  </si>
+  <si>
+    <t>一覧：TestCopy が追加され、選ばれる
+ファイル：TestCopy.bat が作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.10
+処理フロー：2.12</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok、入力なし（保存されている接続情報）
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：成功</t>
+  </si>
+  <si>
+    <t>画面設計：3.10
+処理フロー：2.15</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>画面設計：3.10
+処理フロー：2.14</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：saved-subdomain
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>状態（保存）：完了
+ファイル：ok.bat に saved-subdomain が保存される</t>
+  </si>
+  <si>
+    <t>画面設計：3.10
+処理フロー：2.13</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>サブドメイン：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ログイン名：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+ログイン名：tmp-reload
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「ログイン名」を設定した後で、「再読込」を押します。</t>
+  </si>
+  <si>
+    <t>ログイン名：（保存されている値）
+変えた内容：消える
+状態（再読込）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パスワード：テスト用の値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
+  </si>
+  <si>
+    <t>設定ファイル：ok.bat の KintonePassword が保存される
+状態（保存）：完了</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：ok（既存のグループ名）</t>
+  </si>
+  <si>
+    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+設定ファイル：ok.bat
+グループ名：TestUnsaved</t>
+  </si>
+  <si>
+    <t>「対象のグループ」を設定した後で、「新規作成」を押し、「グループ名」を入力して「OK」を押した後で、「コピー」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「コピー元のグループが存在しません。」
+ファイル：TestUnsaved.bat が作られない</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+サブドメイン：空
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「サブドメイン」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>メッセージ：「エラーが発生しました: サブドメイン・ログイン名・パスワードをすべて入力してください。」
+状態（認証情報）：失敗</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+パスワード：誤った値
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「パスワード」を設定した後で、「テスト接続（認証情報）」を押します。</t>
+  </si>
+  <si>
+    <t>状態（認証情報）：失敗</t>
   </si>
   <si>
     <t>対象のグループ：ng
-スペース識別名：updng</t>
-  </si>
-  <si>
-    <t>状態：成功
-ファイル：checked\dlok_check.xlsx が作られる</t>
-  </si>
-  <si>
-    <t>画面設計 3.7、処理フロー 2.7</t>
-  </si>
-  <si>
-    <t>開いた画面：dlok_check（Excel）</t>
-  </si>
-  <si>
-    <t>画面設計 3.7</t>
-  </si>
-  <si>
-    <t>対象のグループ：ng
-スペース識別名：chkng</t>
-  </si>
-  <si>
-    <t>すべて削除を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「削除対象のログファイルがありません」</t>
-  </si>
-  <si>
-    <t>画面設計 3.8、処理フロー 2.8</t>
-  </si>
-  <si>
-    <t>確認：いいえ</t>
-  </si>
-  <si>
-    <t>確認ダイアログ：ログファイルを削除します
-ログのファイル：残る</t>
-  </si>
-  <si>
-    <t>確認：はい</t>
-  </si>
-  <si>
-    <t>確認ダイアログ：ログファイルを削除します
-ログのファイル：すべて削除される</t>
-  </si>
-  <si>
-    <t>対象のグループ：すべて、ok、ng</t>
-  </si>
-  <si>
-    <t>対象のグループを選びます。</t>
-  </si>
-  <si>
-    <t>表示されるログ：「すべて」を選ぶと ok と ng の両方、「ok」を選ぶと ok のログだけ、「ng」を選ぶと ng のログだけ</t>
-  </si>
-  <si>
-    <t>画面設計 3.8</t>
-  </si>
-  <si>
-    <t>スペース識別名（ログの絞り込み）：すべて、config1、config2</t>
-  </si>
-  <si>
-    <t>スペース識別名（ログの絞り込み）を選びます。</t>
-  </si>
-  <si>
-    <t>表示されるログ：「すべて」を選ぶと両方、「config1」を選ぶと config1 のログだけ、「config2」を選ぶと config2 のログだけ</t>
-  </si>
-  <si>
-    <t>処理のラジオボタンを切り替えます。</t>
-  </si>
-  <si>
-    <t>表示されるログ：選んだ処理のログだけ（ok と ng の両方）</t>
-  </si>
-  <si>
-    <t>ダウンロード先のフォルダ：%BASE_PATH%download2</t>
-  </si>
-  <si>
-    <t>保存を押します。</t>
-  </si>
-  <si>
-    <t>状態：完了
-保存先：bats\common.bat に download2 が保存される</t>
-  </si>
-  <si>
-    <t>画面設計 3.9、処理フロー 2.9</t>
-  </si>
-  <si>
-    <t>ダウンロード先のフォルダ：tmp</t>
-  </si>
-  <si>
-    <t>再読込を押します。</t>
-  </si>
-  <si>
-    <t>入力欄：%BASE_PATH%download（保存されている値）
-変えた内容：消える</t>
-  </si>
-  <si>
-    <t>画面設計 3.9、処理フロー 2.10</t>
-  </si>
-  <si>
-    <t>新しい名前：ok（既存のグループ名）</t>
-  </si>
-  <si>
-    <t>新規作成を押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」
-一覧：追加されない</t>
-  </si>
-  <si>
-    <t>画面設計 3.10、処理フロー 2.11</t>
-  </si>
-  <si>
-    <t>新しい名前：KrgNew</t>
-  </si>
-  <si>
-    <t>一覧：KrgNew が追加され、選ばれる</t>
-  </si>
-  <si>
-    <t>新規作成を押したあと、キャンセルを押します。</t>
-  </si>
-  <si>
-    <t>ファイル：clients\KrgCancel.bat が作られない
-一覧：変わらない</t>
-  </si>
-  <si>
-    <t>新しい名前：KrgUnsaved</t>
-  </si>
-  <si>
-    <t>コピーを押します。</t>
-  </si>
-  <si>
-    <t>メッセージ：「コピー元のグループが存在しません」
-ファイル：clients\KrgUnsaved.bat が作られる</t>
-  </si>
-  <si>
-    <t>画面設計 3.10、処理フロー 2.12</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-新しい名前：KrgCopy</t>
-  </si>
-  <si>
-    <t>一覧：KrgCopy が追加され、選ばれる
-ファイル：clients\KrgCopy.bat が作られる</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-サブドメイン：saved</t>
-  </si>
-  <si>
-    <t>状態：完了
-ファイル：clients\ok.bat に saved が保存される</t>
-  </si>
-  <si>
-    <t>画面設計 3.10、処理フロー 2.13</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-サブドメイン：tmp</t>
-  </si>
-  <si>
-    <t>入力欄：iiglepv0966f（保存されている値）
-変えた内容：消える</t>
-  </si>
-  <si>
-    <t>画面設計 3.10、処理フロー 2.14</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok、入力なし（保存されている接続情報）</t>
-  </si>
-  <si>
-    <t>テスト接続を押します。</t>
-  </si>
-  <si>
-    <t>画面設計 3.10、処理フロー 2.15</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-新しい名前：ok（既存のグループ名）</t>
-  </si>
-  <si>
-    <t>メッセージ：「（入力した名前）は既に存在します。」</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-サブドメイン：空</t>
-  </si>
-  <si>
-    <t>対象のグループ：ok
-パスワード：wrong-password</t>
-  </si>
-  <si>
-    <t>対象のグループ：ng
-パスワード：wrong-password</t>
+パスワード：誤った値
+設定ファイル：ng.bat</t>
   </si>
   <si>
     <t>対象のグループ：ok
 スペースID：3
-テンプレート名：ok</t>
+テンプレート名：ok
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペースID」と「テンプレート名」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
     <t>状態：成功
-ファイル：template\custom\ok_ok.xlsx が作られる</t>
-  </si>
-  <si>
-    <t>画面設計 3.11、処理フロー 2.16</t>
-  </si>
-  <si>
-    <t>開いた画面：ok_ok（Excel）</t>
-  </si>
-  <si>
-    <t>画面設計 3.11</t>
-  </si>
-  <si>
-    <t>対象のグループ、スペースID
-テンプレート名：すべて空</t>
-  </si>
-  <si>
-    <t>メッセージ：「対象のグループ、スペースID、テンプレート名を入力してください」</t>
+ファイル：ok_ok.xlsx が作られる</t>
+  </si>
+  <si>
+    <t>画面設計：3.11
+処理フロー：2.16</t>
+  </si>
+  <si>
+    <t>「対象のグループ」と「スペースID」と「テンプレート名」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
+  </si>
+  <si>
+    <t>状態：成功
+開いた画面：ok_ok（Excel）</t>
+  </si>
+  <si>
+    <t>画面設計：3.11</t>
+  </si>
+  <si>
+    <t>対象のグループ：ng
+スペースID：空
+テンプレート名：空
+設定ファイル：ng.bat</t>
+  </si>
+  <si>
+    <t>メッセージ：「対象のグループ、スペースID、テンプレート名を入力してください。」</t>
   </si>
 </sst>
 </file>
@@ -1005,13 +1380,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8F50C9B-8B0D-4089-9E99-8B124057C5E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E8808B-3BF8-4FCC-9E9C-CBDA71A96E8A}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="18.69921875" customWidth="1"/>
-    <col min="3" max="3" width="10.69921875" customWidth="1"/>
+    <col min="2" max="3" width="18.69921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
@@ -1121,49 +1495,47 @@
         <v>20</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12" xr:uid="{D8F50C9B-8B0D-4089-9E99-8B124057C5E4}"/>
+  <autoFilter ref="A1:C12" xr:uid="{E7E8808B-3BF8-4FCC-9E9C-CBDA71A96E8A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A63DA1-8A5E-4530-887D-ED80C884B652}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24602AB4-18AF-4E9C-93E3-D8BFE3160050}">
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1172,88 +1544,339 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+      <c r="A13" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3" xr:uid="{B8A63DA1-8A5E-4530-887D-ED80C884B652}"/>
+  <autoFilter ref="A1:G14" xr:uid="{24602AB4-18AF-4E9C-93E3-D8BFE3160050}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CA04723-DA52-4D5D-B06B-713DFB053CF9}">
-  <dimension ref="A1:G13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C6555F-8414-4D55-9760-CBA0FE646763}">
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1262,318 +1885,408 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>127</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>128</v>
+        <v>175</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>129</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>131</v>
+        <v>178</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>130</v>
+        <v>177</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>37</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>130</v>
+        <v>184</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>136</v>
+        <v>186</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>137</v>
+        <v>187</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>138</v>
+        <v>188</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="144" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>139</v>
+        <v>178</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>136</v>
+        <v>189</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>141</v>
+        <v>191</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>120</v>
+        <v>192</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>142</v>
+        <v>193</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>143</v>
+        <v>194</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>146</v>
+        <v>190</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>148</v>
+        <v>199</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>93</v>
+        <v>200</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>150</v>
+        <v>201</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>151</v>
+        <v>203</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="90" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>69</v>
+        <v>206</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>149</v>
+        <v>194</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>23</v>
+        <v>168</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>154</v>
+        <v>209</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>148</v>
+        <v>210</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+      <c r="A15" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13" xr:uid="{6CA04723-DA52-4D5D-B06B-713DFB053CF9}"/>
+  <autoFilter ref="A1:G17" xr:uid="{F1C6555F-8414-4D55-9760-CBA0FE646763}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07F9D6E-DC64-4B36-B1F8-3632DDE7D1D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDBF03C-4D26-4B3F-976E-3443AE6AC4ED}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1582,71 +2295,71 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>155</v>
+        <v>221</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>222</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>156</v>
+        <v>223</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>155</v>
+        <v>221</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>225</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>158</v>
+        <v>226</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>159</v>
+        <v>227</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1654,39 +2367,37 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>228</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{F07F9D6E-DC64-4B36-B1F8-3632DDE7D1D9}"/>
+  <autoFilter ref="A1:G4" xr:uid="{BEDBF03C-4D26-4B3F-976E-3443AE6AC4ED}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF2EB034-3901-4859-8B5D-8AC8473A78E0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476DAE4D-946F-4E81-8CB7-DE299C1D9163}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1695,71 +2406,71 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1770,19 +2481,19 @@
         <v>41</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1790,22 +2501,22 @@
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1813,22 +2524,22 @@
         <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -1839,36 +2550,34 @@
         <v>47</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{EF2EB034-3901-4859-8B5D-8AC8473A78E0}"/>
+  <autoFilter ref="A1:G7" xr:uid="{476DAE4D-946F-4E81-8CB7-DE299C1D9163}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4371BDB-1634-48AC-AFC4-53E0821441DF}">
-  <dimension ref="A1:G10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926C85F9-2889-4692-ABE3-33F8A6414DF3}">
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1877,117 +2586,117 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>49</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1995,22 +2704,22 @@
         <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -2018,22 +2727,22 @@
         <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="360" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -2041,22 +2750,22 @@
         <v>40</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>18</v>
       </c>
@@ -2064,62 +2773,37 @@
         <v>40</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10" xr:uid="{B4371BDB-1634-48AC-AFC4-53E0821441DF}"/>
+  <autoFilter ref="A1:G9" xr:uid="{926C85F9-2889-4692-ABE3-33F8A6414DF3}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B47E84BA-7759-477A-B660-7A2B35411083}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B55D71-0C02-4FAA-86E4-8EA50B8E4FBE}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2128,71 +2812,71 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2200,22 +2884,22 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2223,39 +2907,37 @@
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{B47E84BA-7759-477A-B660-7A2B35411083}"/>
+  <autoFilter ref="A1:G5" xr:uid="{92B55D71-0C02-4FAA-86E4-8EA50B8E4FBE}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A730DC49-937B-49FB-AC66-4BE4ED439C97}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8244F30-D901-41F7-9495-579D83CA6612}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2264,71 +2946,71 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2336,22 +3018,22 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2359,39 +3041,37 @@
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{A730DC49-937B-49FB-AC66-4BE4ED439C97}"/>
+  <autoFilter ref="A1:G5" xr:uid="{A8244F30-D901-41F7-9495-579D83CA6612}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF84B593-1D90-44E3-8E03-C548867561BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1782A9E0-0294-40CD-8F76-4E083E7AD04D}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2400,71 +3080,71 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -2472,22 +3152,22 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="342" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2495,22 +3175,22 @@
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="378" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -2518,39 +3198,37 @@
         <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{AF84B593-1D90-44E3-8E03-C548867561BA}"/>
+  <autoFilter ref="A1:G6" xr:uid="{1782A9E0-0294-40CD-8F76-4E083E7AD04D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C049101B-C07A-47BD-AE85-FEECA21EE90E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B78AC1-0196-410C-8253-C6D828447D1A}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2559,68 +3237,68 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
@@ -2631,22 +3309,22 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2654,39 +3332,37 @@
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{C049101B-C07A-47BD-AE85-FEECA21EE90E}"/>
+  <autoFilter ref="A1:G5" xr:uid="{15B78AC1-0196-410C-8253-C6D828447D1A}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CFEC446-5B8B-4116-B077-4F7AD7289CC0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE3AAF2-ABEF-4113-9393-C3C34B10D3A3}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2695,68 +3371,68 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
@@ -2767,22 +3443,22 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2790,39 +3466,37 @@
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{2CFEC446-5B8B-4116-B077-4F7AD7289CC0}"/>
+  <autoFilter ref="A1:G5" xr:uid="{8DE3AAF2-ABEF-4113-9393-C3C34B10D3A3}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{495A2F42-D793-46FE-8656-BF6F6AB47715}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68627B54-62FC-4583-833E-69EAFC3FE31C}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
     <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="3" width="50.69921875" customWidth="1"/>
-    <col min="4" max="4" width="45.69921875" customWidth="1"/>
-    <col min="5" max="5" width="75.69921875" customWidth="1"/>
-    <col min="6" max="6" width="28.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
     <col min="7" max="7" width="12.69921875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2831,164 +3505,164 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="144" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="270" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="126" x14ac:dyDescent="0.45">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{495A2F42-D793-46FE-8656-BF6F6AB47715}"/>
+  <autoFilter ref="A1:G7" xr:uid="{68627B54-62FC-4583-833E-69EAFC3FE31C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F14DB658-970B-4161-B8F8-15012C21880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F193DDBF-4E2C-4842-A4BD-15CD00F0F072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{255AE821-CC83-4DEC-8291-52AC6F6926E6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F82ADF64-7519-40A1-9F0E-6F36D5641E6B}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -76,40 +76,40 @@
     <t>実行（一括実行）</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>実行（スペース作成）</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>実行（スペースダウンロード）</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>実行（設定ファイル作成）</t>
+  </si>
+  <si>
+    <t>実行（スペース更新）</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>実行（スペース確認）</t>
+  </si>
+  <si>
+    <t>ログ</t>
+  </si>
+  <si>
     <t>9</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>実行（スペース作成）</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>実行（スペースダウンロード）</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>実行（設定ファイル作成）</t>
-  </si>
-  <si>
-    <t>実行（スペース更新）</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>実行（スペース確認）</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>ログ</t>
   </si>
   <si>
     <t>環境設定（共通）</t>
@@ -226,12 +226,12 @@
     <t>「対象のグループ」と「スペース識別名」と「スペーステンプレートID」と「設定テンプレート名（基本）」を設定した後で、「表示／隠す」を押した後で、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態：成功
-状態（スペースの作成）：成功
+    <t>状態（スペースの作成）：成功
 状態（スペースのダウンロード）：成功
 状態（設定ファイルの作成）：成功
 状態（スペースの更新）：成功
-状態（スペースの確認）：成功</t>
+状態（スペースの確認）：成功
+状態：成功</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -278,7 +278,7 @@
   <si>
     <t>状態：成功
 状態（スペースの確認）：スキップ
-状態（スペースのダウンロード）：成功または失敗</t>
+状態（スペースのダウンロード）：成功</t>
   </si>
   <si>
     <t>メッセージ：「スペース識別名 を設定してください。」</t>
@@ -335,9 +335,9 @@
 設定ファイル：ok.bat</t>
   </si>
   <si>
-    <t>状態：失敗
-状態（スペースの作成）：失敗
-状態（設定ファイルの作成）：表示されない</t>
+    <t>状態（スペースの作成）：失敗
+状態（設定ファイルの作成）：表示されない
+状態：失敗</t>
   </si>
   <si>
     <t>対象のグループ：ng
@@ -376,7 +376,7 @@
     <t>「対象のグループ」と「スペース識別名」と「スペーステンプレートID」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：TestSpace（ブラウザ）</t>
+    <t>開く：テスト用のスペース（TestSpace）</t>
   </si>
   <si>
     <t>画面設計：3.3</t>
@@ -404,7 +404,7 @@
   </si>
   <si>
     <t>状態：成功
-ファイル：TestSpace_download.xlsx が作られる</t>
+ファイル：TestSpace_download.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -414,7 +414,7 @@
     <t>「対象のグループ」と「スペース識別名」と「スペースID」を設定した後で、「実行」を押した後で、「開く」を押します。</t>
   </si>
   <si>
-    <t>開いた画面：TestSpace_download（Excel）</t>
+    <t>開く：TestSpace_download.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4</t>
@@ -444,7 +444,7 @@
   </si>
   <si>
     <t>状態：成功または警告
-ファイル：TestSpace_config.xlsx が作られる</t>
+ファイル：TestSpace_config.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.5
@@ -455,7 +455,7 @@
   </si>
   <si>
     <t>状態：成功または警告
-開いた画面：TestSpace_config（Excel）</t>
+開く：TestSpace_config.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.5</t>
@@ -506,7 +506,7 @@
   </si>
   <si>
     <t>状態：成功
-開いた画面：TestSpace（ブラウザ）</t>
+開く：テスト用のスペース（TestSpace）</t>
   </si>
   <si>
     <t>画面設計：3.6</t>
@@ -523,7 +523,7 @@
   </si>
   <si>
     <t>状態：成功
-ファイル：TestSpace_check.xlsx が作られる</t>
+ファイル：TestSpace_check.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -531,7 +531,7 @@
   </si>
   <si>
     <t>状態：成功
-開いた画面：TestSpace_check（Excel）</t>
+開く：TestSpace_check.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.7</t>
@@ -800,7 +800,7 @@
   </si>
   <si>
     <t>一覧：TestCopy が追加され、選ばれる
-ファイル：TestCopy.bat が作られる</t>
+ファイル：TestCopy.bat</t>
   </si>
   <si>
     <t>画面設計：3.10
@@ -958,7 +958,7 @@
   </si>
   <si>
     <t>状態：成功
-ファイル：ok_ok.xlsx が作られる</t>
+ファイル：ok_ok.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.11
@@ -969,7 +969,7 @@
   </si>
   <si>
     <t>状態：成功
-開いた画面：ok_ok（Excel）</t>
+開く：ok_ok.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.11</t>
@@ -1380,7 +1380,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E8808B-3BF8-4FCC-9E9C-CBDA71A96E8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EA4A4A-0B64-499E-873A-EA049C583611}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>5</v>
@@ -1489,7 +1489,7 @@
     </row>
     <row r="10" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>20</v>
@@ -1521,14 +1521,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12" xr:uid="{E7E8808B-3BF8-4FCC-9E9C-CBDA71A96E8A}"/>
+  <autoFilter ref="A1:C12" xr:uid="{02EA4A4A-0B64-499E-873A-EA049C583611}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24602AB4-18AF-4E9C-93E3-D8BFE3160050}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1D2CF1-F20C-417D-93D0-A8F4F38811D6}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="9" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>33</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="10" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>33</v>
@@ -1862,14 +1862,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14" xr:uid="{24602AB4-18AF-4E9C-93E3-D8BFE3160050}"/>
+  <autoFilter ref="A1:G14" xr:uid="{DF1D2CF1-F20C-417D-93D0-A8F4F38811D6}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C6555F-8414-4D55-9760-CBA0FE646763}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB357C00-A3E1-4A6C-8D7D-7BF543A277C7}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2066,7 +2066,7 @@
     </row>
     <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>33</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="10" spans="1:7" ht="180" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>33</v>
@@ -2272,14 +2272,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17" xr:uid="{F1C6555F-8414-4D55-9760-CBA0FE646763}"/>
+  <autoFilter ref="A1:G17" xr:uid="{AB357C00-A3E1-4A6C-8D7D-7BF543A277C7}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDBF03C-4D26-4B3F-976E-3443AE6AC4ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A254EA26-E065-4F34-93DC-6A097BACBB7C}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2383,14 +2383,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{BEDBF03C-4D26-4B3F-976E-3443AE6AC4ED}"/>
+  <autoFilter ref="A1:G4" xr:uid="{A254EA26-E065-4F34-93DC-6A097BACBB7C}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476DAE4D-946F-4E81-8CB7-DE299C1D9163}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDAF1AD7-0B60-410C-969E-1E26D2C1CD83}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2563,14 +2563,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{476DAE4D-946F-4E81-8CB7-DE299C1D9163}"/>
+  <autoFilter ref="A1:G7" xr:uid="{FDAF1AD7-0B60-410C-969E-1E26D2C1CD83}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{926C85F9-2889-4692-ABE3-33F8A6414DF3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4235499B-8A8B-4533-B0EE-9EEAB9E8A68E}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2767,7 +2767,7 @@
     </row>
     <row r="9" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>40</v>
@@ -2789,14 +2789,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{926C85F9-2889-4692-ABE3-33F8A6414DF3}"/>
+  <autoFilter ref="A1:G9" xr:uid="{4235499B-8A8B-4533-B0EE-9EEAB9E8A68E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92B55D71-0C02-4FAA-86E4-8EA50B8E4FBE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E19DAF-C2B1-4CD9-87AE-D7FD29014F88}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2923,14 +2923,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{92B55D71-0C02-4FAA-86E4-8EA50B8E4FBE}"/>
+  <autoFilter ref="A1:G5" xr:uid="{72E19DAF-C2B1-4CD9-87AE-D7FD29014F88}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8244F30-D901-41F7-9495-579D83CA6612}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59520F0C-91CE-4566-9A14-5BE69BFC5BBD}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3057,14 +3057,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{A8244F30-D901-41F7-9495-579D83CA6612}"/>
+  <autoFilter ref="A1:G5" xr:uid="{59520F0C-91CE-4566-9A14-5BE69BFC5BBD}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1782A9E0-0294-40CD-8F76-4E083E7AD04D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8CED8E-0883-45CA-A14B-B6FCA2EB8592}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3214,14 +3214,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{1782A9E0-0294-40CD-8F76-4E083E7AD04D}"/>
+  <autoFilter ref="A1:G6" xr:uid="{8B8CED8E-0883-45CA-A14B-B6FCA2EB8592}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15B78AC1-0196-410C-8253-C6D828447D1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54481657-EB2B-476D-8C28-8A3C05D93D72}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3348,14 +3348,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{15B78AC1-0196-410C-8253-C6D828447D1A}"/>
+  <autoFilter ref="A1:G5" xr:uid="{54481657-EB2B-476D-8C28-8A3C05D93D72}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DE3AAF2-ABEF-4113-9393-C3C34B10D3A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF459E7B-B52D-4B09-96D8-B8E19C559D90}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3482,14 +3482,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{8DE3AAF2-ABEF-4113-9393-C3C34B10D3A3}"/>
+  <autoFilter ref="A1:G5" xr:uid="{FF459E7B-B52D-4B09-96D8-B8E19C559D90}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68627B54-62FC-4583-833E-69EAFC3FE31C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCFEEBE6-B570-44CA-AB07-37C64426DAAE}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3662,7 +3662,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{68627B54-62FC-4583-833E-69EAFC3FE31C}"/>
+  <autoFilter ref="A1:G7" xr:uid="{BCFEEBE6-B570-44CA-AB07-37C64426DAAE}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F193DDBF-4E2C-4842-A4BD-15CD00F0F072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60963DFB-A85B-4904-9FB6-6C81BCBA4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F82ADF64-7519-40A1-9F0E-6F36D5641E6B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F234BE0E-2D3F-4D18-ADA2-10B087CA09D1}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'2.6 実行（スペース更新）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'2.7 実行（スペース確認）'!$A$1:$G$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'2.8 ログ'!$A$1:$G$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（共通）'!$A$1:$G$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'2.9 環境設定（共通）'!$A$1:$G$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">一覧!$A$1:$C$12</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="229">
   <si>
     <t>通番</t>
   </si>
@@ -115,7 +115,7 @@
     <t>環境設定（共通）</t>
   </si>
   <si>
-    <t>13</t>
+    <t>12</t>
   </si>
   <si>
     <t>10</t>
@@ -162,7 +162,10 @@
     <t>「対象のグループ」と「実行一覧ファイル」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態：終了（成功-1件、警告-0件、失敗/スキップ-1件）</t>
+    <t>状態：終了（成功-1件、警告-0件、失敗/スキップ-1件）
+ダウンロード結果：TestSpace_download.xlsx
+設定ファイル：TestSpace_config.xlsx
+確認結果：TestSpace_check.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.1
@@ -231,7 +234,10 @@
 状態（設定ファイルの作成）：成功
 状態（スペースの更新）：成功
 状態（スペースの確認）：成功
-状態：成功</t>
+状態：成功
+ダウンロード結果：TestSpace_download.xlsx
+設定ファイル：TestSpace_config.xlsx
+確認結果：TestSpace_check.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.2
@@ -276,9 +282,9 @@
     <t>「対象のグループ」と「スペース識別名」と「スペーステンプレートID」と「設定テンプレート名（基本）」を設定した後で、「表示／隠す」を押した後で、「スペースの確認」のチェックを外して、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態：成功
-状態（スペースの確認）：スキップ
-状態（スペースのダウンロード）：成功</t>
+    <t>状態（スペースの確認）：スキップ
+状態（スペースのダウンロード）：成功
+状態：成功</t>
   </si>
   <si>
     <t>メッセージ：「スペース識別名 を設定してください。」</t>
@@ -404,7 +410,7 @@
   </si>
   <si>
     <t>状態：成功
-ファイル：TestSpace_download.xlsx</t>
+ダウンロード結果：TestSpace_download.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.4
@@ -444,7 +450,7 @@
   </si>
   <si>
     <t>状態：成功または警告
-ファイル：TestSpace_config.xlsx</t>
+設定ファイル：TestSpace_config.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.5
@@ -523,7 +529,7 @@
   </si>
   <si>
     <t>状態：成功
-ファイル：TestSpace_check.xlsx</t>
+確認結果：TestSpace_check.xlsx</t>
   </si>
   <si>
     <t>画面設計：3.7
@@ -621,7 +627,7 @@
   </si>
   <si>
     <t>状態（保存）：完了
-保存先：common.bat に saved-download-path が保存される</t>
+保存先：common.bat に CommonDownloadPath=saved-download-path が保存される</t>
   </si>
   <si>
     <t>画面設計：3.9
@@ -649,7 +655,7 @@
     <t>「設定テンプレート（基本）ファイルのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-base-template が保存される
+    <t>設定ファイル：common.bat に CommonBaseTemplatePath=saved-base-template が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -672,7 +678,7 @@
     <t>「設定テンプレート（カスタム）ファイルのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-custom-template が保存される
+    <t>設定ファイル：common.bat に CommonCustomTemplatePath=saved-custom-template が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -695,7 +701,7 @@
     <t>「設定ファイルのフォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-config-folder が保存される
+    <t>設定ファイル：common.bat に CommonConfigPath=saved-config-folder が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -718,7 +724,7 @@
     <t>「チェック結果の出力先フォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-check-output が保存される
+    <t>設定ファイル：common.bat に CommonCheckOutputPath=saved-check-output が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -741,11 +747,8 @@
     <t>「ログの出力先フォルダ」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：common.bat に saved-log-folder が保存される
+    <t>設定ファイル：common.bat に CommonLogPath=saved-log-folder が保存される
 状態（保存）：完了</t>
-  </si>
-  <si>
-    <t>12</t>
   </si>
   <si>
     <t>ログの出力先フォルダ：tmp-reload
@@ -760,12 +763,6 @@
 状態（再読込）：完了</t>
   </si>
   <si>
-    <t>「再読込」を押します。</t>
-  </si>
-  <si>
-    <t>状態（再読込）：完了</t>
-  </si>
-  <si>
     <t>対象のグループ：ok
 設定ファイル：ok.bat
 グループ名：TestNew</t>
@@ -824,6 +821,9 @@
     <t>「対象のグループ」を設定した後で、「再読込」を押します。</t>
   </si>
   <si>
+    <t>状態（再読込）：完了</t>
+  </si>
+  <si>
     <t>画面設計：3.10
 処理フロー：2.14</t>
   </si>
@@ -837,7 +837,7 @@
   </si>
   <si>
     <t>状態（保存）：完了
-ファイル：ok.bat に saved-subdomain が保存される</t>
+ファイル：ok.bat に KintoneSubdomain=saved-subdomain が保存される</t>
   </si>
   <si>
     <t>画面設計：3.10
@@ -858,14 +858,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-ログイン名：テスト用の値
+ログイン名：saved-login
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「ログイン名」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintoneLoginName が保存される
+    <t>設定ファイル：ok.bat に KintoneLoginName=saved-login が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -883,14 +883,14 @@
   </si>
   <si>
     <t>対象のグループ：ok
-パスワード：テスト用の値
+パスワード：saved-pass
 設定ファイル：ok.bat</t>
   </si>
   <si>
     <t>「対象のグループ」と「パスワード」を設定した後で、「保存」を押します。</t>
   </si>
   <si>
-    <t>設定ファイル：ok.bat の KintonePassword が保存される
+    <t>設定ファイル：ok.bat に KintonePassword=saved-pass が保存される
 状態（保存）：完了</t>
   </si>
   <si>
@@ -912,6 +912,9 @@
   <si>
     <t>メッセージ：「コピー元のグループが存在しません。」
 ファイル：TestUnsaved.bat が作られない</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>14</t>
@@ -1380,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02EA4A4A-0B64-499E-873A-EA049C583611}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF9DCD1-7A7B-4D4B-A7B1-5B6AE6736D9F}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1521,15 +1524,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12" xr:uid="{02EA4A4A-0B64-499E-873A-EA049C583611}"/>
+  <autoFilter ref="A1:C12" xr:uid="{CBF9DCD1-7A7B-4D4B-A7B1-5B6AE6736D9F}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1D2CF1-F20C-417D-93D0-A8F4F38811D6}">
-  <dimension ref="A1:G14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A20E9F4-24F7-4F61-815C-37CC1523942D}">
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.69921875" customWidth="1"/>
@@ -1562,7 +1565,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1654,7 +1657,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1700,7 +1703,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -1746,7 +1749,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="216" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>19</v>
       </c>
@@ -1792,7 +1795,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>25</v>
       </c>
@@ -1817,19 +1820,19 @@
     </row>
     <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>171</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>140</v>
@@ -1838,38 +1841,15 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="90" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G14" xr:uid="{DF1D2CF1-F20C-417D-93D0-A8F4F38811D6}"/>
+  <autoFilter ref="A1:G13" xr:uid="{8A20E9F4-24F7-4F61-815C-37CC1523942D}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB357C00-A3E1-4A6C-8D7D-7BF543A277C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A317277E-00EC-403D-AD8A-CFD55FF172C2}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1911,16 +1891,16 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>174</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>38</v>
@@ -1934,16 +1914,16 @@
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>38</v>
@@ -1957,16 +1937,16 @@
         <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>38</v>
@@ -1980,16 +1960,16 @@
         <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
@@ -2003,22 +1983,22 @@
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
@@ -2026,16 +2006,16 @@
         <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>38</v>
@@ -2049,22 +2029,22 @@
         <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -2072,16 +2052,16 @@
         <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>38</v>
@@ -2095,22 +2075,22 @@
         <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="F10" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
@@ -2118,16 +2098,16 @@
         <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>38</v>
@@ -2141,16 +2121,16 @@
         <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>38</v>
@@ -2158,22 +2138,22 @@
     </row>
     <row r="13" spans="1:7" ht="288" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>168</v>
+        <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>38</v>
@@ -2181,22 +2161,22 @@
     </row>
     <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
@@ -2204,22 +2184,22 @@
     </row>
     <row r="15" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>38</v>
@@ -2227,22 +2207,22 @@
     </row>
     <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>38</v>
@@ -2256,30 +2236,30 @@
         <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17" xr:uid="{AB357C00-A3E1-4A6C-8D7D-7BF543A277C7}"/>
+  <autoFilter ref="A1:G17" xr:uid="{A317277E-00EC-403D-AD8A-CFD55FF172C2}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A254EA26-E065-4F34-93DC-6A097BACBB7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7724B3-6100-43A0-9445-E1680002DF04}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2321,16 +2301,16 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>38</v>
@@ -2344,16 +2324,16 @@
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>38</v>
@@ -2367,30 +2347,30 @@
         <v>40</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{A254EA26-E065-4F34-93DC-6A097BACBB7C}"/>
+  <autoFilter ref="A1:G4" xr:uid="{0B7724B3-6100-43A0-9445-E1680002DF04}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDAF1AD7-0B60-410C-969E-1E26D2C1CD83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D0D0C5-68CA-4460-8DD0-4D3D8275042B}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2424,7 +2404,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2563,14 +2543,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{FDAF1AD7-0B60-410C-969E-1E26D2C1CD83}"/>
+  <autoFilter ref="A1:G7" xr:uid="{18D0D0C5-68CA-4460-8DD0-4D3D8275042B}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4235499B-8A8B-4533-B0EE-9EEAB9E8A68E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F355FFCE-8B7B-438E-B5F1-AA6561A4D836}">
   <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2789,14 +2769,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{4235499B-8A8B-4533-B0EE-9EEAB9E8A68E}"/>
+  <autoFilter ref="A1:G9" xr:uid="{F355FFCE-8B7B-438E-B5F1-AA6561A4D836}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72E19DAF-C2B1-4CD9-87AE-D7FD29014F88}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CC17DB-7B23-4E30-8531-D2454600408E}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2923,14 +2903,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{72E19DAF-C2B1-4CD9-87AE-D7FD29014F88}"/>
+  <autoFilter ref="A1:G5" xr:uid="{D4CC17DB-7B23-4E30-8531-D2454600408E}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59520F0C-91CE-4566-9A14-5BE69BFC5BBD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76BB6E3F-CA6D-4EA0-B34E-19A7718782DA}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3057,14 +3037,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{59520F0C-91CE-4566-9A14-5BE69BFC5BBD}"/>
+  <autoFilter ref="A1:G5" xr:uid="{76BB6E3F-CA6D-4EA0-B34E-19A7718782DA}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B8CED8E-0883-45CA-A14B-B6FCA2EB8592}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31656121-B22C-4CD9-92D9-A728CD1267EB}">
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3214,14 +3194,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{8B8CED8E-0883-45CA-A14B-B6FCA2EB8592}"/>
+  <autoFilter ref="A1:G6" xr:uid="{31656121-B22C-4CD9-92D9-A728CD1267EB}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54481657-EB2B-476D-8C28-8A3C05D93D72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21DB6F4-EE95-421C-8B0F-B2C59112E4FC}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3348,14 +3328,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{54481657-EB2B-476D-8C28-8A3C05D93D72}"/>
+  <autoFilter ref="A1:G5" xr:uid="{A21DB6F4-EE95-421C-8B0F-B2C59112E4FC}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF459E7B-B52D-4B09-96D8-B8E19C559D90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D8D2E7-902F-4325-A8EE-D876BD6887A3}">
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3482,14 +3462,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{FF459E7B-B52D-4B09-96D8-B8E19C559D90}"/>
+  <autoFilter ref="A1:G5" xr:uid="{43D8D2E7-902F-4325-A8EE-D876BD6887A3}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCFEEBE6-B570-44CA-AB07-37C64426DAAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A04CED-8128-4DB3-8BA2-EE29F0018424}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -3662,7 +3642,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{BCFEEBE6-B570-44CA-AB07-37C64426DAAE}"/>
+  <autoFilter ref="A1:G7" xr:uid="{55A04CED-8128-4DB3-8BA2-EE29F0018424}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
+++ b/tool/kintone-resourse-generator/doc/03_結合テスト/テスト仕様書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\project_management\tool\kintone-resourse-generator\doc\03_結合テスト\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{60963DFB-A85B-4904-9FB6-6C81BCBA4D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C4C781BC-344E-4F76-8E2F-20EC5235D1C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F234BE0E-2D3F-4D18-ADA2-10B087CA09D1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DD0DE3A8-20AF-4340-B84F-B423F7BBCC4B}"/>
   </bookViews>
   <sheets>
     <sheet name="一覧" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <sheet name="2.11 環境設定（テンプレート）" sheetId="12" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（複数実行）'!$A$1:$G$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2.1 実行（複数実行）'!$A$1:$G$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'2.10 環境設定（グループ別）'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'2.11 環境設定（テンプレート）'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.2 実行（一括実行）'!$A$1:$G$9</definedName>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="232">
   <si>
     <t>通番</t>
   </si>
@@ -67,40 +67,40 @@
     <t>実行（複数実行）</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>実行（一括実行）</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>実行（スペース作成）</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>実行（スペースダウンロード）</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>実行（設定ファイル作成）</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>実行（一括実行）</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>実行（スペース作成）</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>実行（スペースダウンロード）</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>実行（設定ファイル作成）</t>
-  </si>
-  <si>
     <t>実行（スペース更新）</t>
-  </si>
-  <si>
-    <t>7</t>
   </si>
   <si>
     <t>実行（スペース確認）</t>
@@ -162,7 +162,7 @@
     <t>「対象のグループ」と「実行一覧ファイル」を設定した後で、「実行」を押します。</t>
   </si>
   <si>
-    <t>状態：終了（成功-1件、警告-0件、失敗/スキップ-1件）
+    <t>状態：終了（成功-1件、警告-0件、失敗/スキップ-0件）
 ダウンロード結果：TestSpace_download.xlsx
 設定ファイル：TestSpace_config.xlsx
 確認結果：TestSpace_check.xlsx</t>
@@ -175,7 +175,26 @@
     <t/>
   </si>
   <si>
-    <t>状態：終了（件数）が表示される</t>
+    <t>対象のグループ：ok
+実行一覧ファイル：multiple1.xlsx
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態：終了（成功-2件、警告-0件、失敗/スキップ-0件）
+ダウンロード結果：TestSpace1_download.xlsx、TestSpace2_download.xlsx
+設定ファイル：TestSpace1_config.xlsx、TestSpace2_config.xlsx
+確認結果：TestSpace1_check.xlsx、TestSpace2_check.xlsx</t>
+  </si>
+  <si>
+    <t>対象のグループ：ok
+実行一覧ファイル：multiple2.xlsx
+設定ファイル：ok.bat</t>
+  </si>
+  <si>
+    <t>状態：終了（成功-1件、警告-1件、失敗/スキップ-0件）
+ダウンロード結果：TestSpace1_download.xlsx、TestSpace2_download.xlsx
+設定ファイル：TestSpace1_config.xlsx、TestSpace2_config.xlsx
+確認結果：TestSpace1_check.xlsx、TestSpace2_check.xlsx</t>
   </si>
   <si>
     <t>異常系</t>
@@ -1383,7 +1402,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBF9DCD1-7A7B-4D4B-A7B1-5B6AE6736D9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{803057E4-4E5F-41F2-99BC-5C05E9F5A9A3}">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1459,10 +1478,10 @@
     </row>
     <row r="7" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
@@ -1470,7 +1489,7 @@
     </row>
     <row r="8" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
@@ -1487,7 +1506,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="36" x14ac:dyDescent="0.45">
@@ -1524,14 +1543,14 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C12" xr:uid="{CBF9DCD1-7A7B-4D4B-A7B1-5B6AE6736D9F}"/>
+  <autoFilter ref="A1:C12" xr:uid="{803057E4-4E5F-41F2-99BC-5C05E9F5A9A3}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A20E9F4-24F7-4F61-815C-37CC1523942D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33DE6031-23DA-4375-A80B-9DDBAE949263}">
   <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1573,16 +1592,16 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>38</v>
@@ -1596,16 +1615,16 @@
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>38</v>
@@ -1619,16 +1638,16 @@
         <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>38</v>
@@ -1642,16 +1661,16 @@
         <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
@@ -1665,16 +1684,16 @@
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>38</v>
@@ -1682,22 +1701,22 @@
     </row>
     <row r="7" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>38</v>
@@ -1705,22 +1724,22 @@
     </row>
     <row r="8" spans="1:7" ht="252" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>38</v>
@@ -1734,16 +1753,16 @@
         <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>38</v>
@@ -1757,16 +1776,16 @@
         <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>38</v>
@@ -1780,16 +1799,16 @@
         <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>38</v>
@@ -1803,16 +1822,16 @@
         <v>33</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>38</v>
@@ -1826,30 +1845,30 @@
         <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G13" xr:uid="{8A20E9F4-24F7-4F61-815C-37CC1523942D}"/>
+  <autoFilter ref="A1:G13" xr:uid="{33DE6031-23DA-4375-A80B-9DDBAE949263}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A317277E-00EC-403D-AD8A-CFD55FF172C2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E579EE32-5938-474D-869D-2515E3604DC1}">
   <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1891,16 +1910,16 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>38</v>
@@ -1914,16 +1933,16 @@
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>38</v>
@@ -1937,16 +1956,16 @@
         <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>38</v>
@@ -1960,16 +1979,16 @@
         <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
@@ -1983,16 +2002,16 @@
         <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>38</v>
@@ -2000,22 +2019,22 @@
     </row>
     <row r="7" spans="1:7" ht="216" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>38</v>
@@ -2023,22 +2042,22 @@
     </row>
     <row r="8" spans="1:7" ht="198" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>38</v>
@@ -2052,16 +2071,16 @@
         <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>38</v>
@@ -2075,16 +2094,16 @@
         <v>33</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>38</v>
@@ -2098,16 +2117,16 @@
         <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>38</v>
@@ -2118,19 +2137,19 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>38</v>
@@ -2141,19 +2160,19 @@
         <v>21</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>38</v>
@@ -2161,22 +2180,22 @@
     </row>
     <row r="14" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
@@ -2184,22 +2203,22 @@
     </row>
     <row r="15" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>38</v>
@@ -2207,22 +2226,22 @@
     </row>
     <row r="16" spans="1:7" ht="234" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>38</v>
@@ -2233,33 +2252,33 @@
         <v>24</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17" xr:uid="{A317277E-00EC-403D-AD8A-CFD55FF172C2}"/>
+  <autoFilter ref="A1:G17" xr:uid="{E579EE32-5938-474D-869D-2515E3604DC1}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B7724B3-6100-43A0-9445-E1680002DF04}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D61BD6-AF92-446A-B982-D26E4DD6C7AF}">
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2301,16 +2320,16 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>38</v>
@@ -2324,16 +2343,16 @@
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>38</v>
@@ -2344,33 +2363,1155 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4" xr:uid="{0B7724B3-6100-43A0-9445-E1680002DF04}"/>
+  <autoFilter ref="A1:G4" xr:uid="{B4D61BD6-AF92-446A-B982-D26E4DD6C7AF}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18D0D0C5-68CA-4460-8DD0-4D3D8275042B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E80450F-2844-483B-8688-C6F2EC11F905}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G8" xr:uid="{5E80450F-2844-483B-8688-C6F2EC11F905}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92E489B9-91FB-475F-B15F-733388B69395}">
+  <dimension ref="A1:G9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G9" xr:uid="{92E489B9-91FB-475F-B15F-733388B69395}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBC080FC-D796-4B18-840C-84A667AE14A5}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5" xr:uid="{EBC080FC-D796-4B18-840C-84A667AE14A5}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873A3827-CD6F-4D08-A8E3-C9AFD919C9D6}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5" xr:uid="{873A3827-CD6F-4D08-A8E3-C9AFD919C9D6}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DA6152E-3A7D-4E52-9818-FFD2A8BF52FF}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="324" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="342" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="378" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G6" xr:uid="{5DA6152E-3A7D-4E52-9818-FFD2A8BF52FF}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF76072-D7FE-43B1-8230-11829C699D4A}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5" xr:uid="{BCF76072-D7FE-43B1-8230-11829C699D4A}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F1AB5A-A4DB-40CC-8F71-3399C86CD3CD}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="8.69921875" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" customWidth="1"/>
+    <col min="3" max="5" width="70.69921875" customWidth="1"/>
+    <col min="6" max="6" width="20.69921875" customWidth="1"/>
+    <col min="7" max="7" width="12.69921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G5" xr:uid="{E0F1AB5A-A4DB-40CC-8F71-3399C86CD3CD}"/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FDA6C6B-813A-4EDA-A3BF-3D22DC02D1E4}">
   <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2404,7 +3545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -2412,22 +3553,22 @@
         <v>33</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="180" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -2435,242 +3576,62 @@
         <v>33</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="198" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7" ht="324" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>127</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>128</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="180" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{18D0D0C5-68CA-4460-8DD0-4D3D8275042B}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F355FFCE-8B7B-438E-B5F1-AA6561A4D836}">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>52</v>
+        <v>126</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
@@ -2681,938 +3642,19 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>62</v>
+        <v>131</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>132</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G9" xr:uid="{F355FFCE-8B7B-438E-B5F1-AA6561A4D836}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4CC17DB-7B23-4E30-8531-D2454600408E}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="252" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{D4CC17DB-7B23-4E30-8531-D2454600408E}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76BB6E3F-CA6D-4EA0-B34E-19A7718782DA}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="288" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="198" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="234" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{76BB6E3F-CA6D-4EA0-B34E-19A7718782DA}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31656121-B22C-4CD9-92D9-A728CD1267EB}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="324" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="342" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="378" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G6" xr:uid="{31656121-B22C-4CD9-92D9-A728CD1267EB}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21DB6F4-EE95-421C-8B0F-B2C59112E4FC}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{A21DB6F4-EE95-421C-8B0F-B2C59112E4FC}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D8D2E7-902F-4325-A8EE-D876BD6887A3}">
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="162" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="180" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G5" xr:uid="{43D8D2E7-902F-4325-A8EE-D876BD6887A3}"/>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55A04CED-8128-4DB3-8BA2-EE29F0018424}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="8.69921875" customWidth="1"/>
-    <col min="2" max="2" width="10.69921875" customWidth="1"/>
-    <col min="3" max="5" width="70.69921875" customWidth="1"/>
-    <col min="6" max="6" width="20.69921875" customWidth="1"/>
-    <col min="7" max="7" width="12.69921875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="324" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="306" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="270" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="324" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="409.6" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>38</v>
@@ -3620,29 +3662,29 @@
     </row>
     <row r="7" spans="1:7" ht="270" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7" xr:uid="{55A04CED-8128-4DB3-8BA2-EE29F0018424}"/>
+  <autoFilter ref="A1:G7" xr:uid="{7FDA6C6B-813A-4EDA-A3BF-3D22DC02D1E4}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
